--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,7 +513,7 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
 </t>
   </si>
   <si>
@@ -529,7 +529,7 @@
     <t>identityReliability</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-ident-reliability}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-ident-reliability}
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
     <t>deathPlace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-death-place}
 </t>
   </si>
   <si>
@@ -561,7 +561,7 @@
     <t>identityMethodCollection</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-identity-method-collection}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-identity-method-collection}
 </t>
   </si>
   <si>
@@ -577,7 +577,7 @@
     <t>birthdateUpdateIndicator</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birthdate-update-indicator}
 </t>
   </si>
   <si>
@@ -642,7 +642,7 @@
     <t>Patient.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
@@ -1115,7 +1115,7 @@
     <t>Patient.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
@@ -1402,7 +1402,7 @@
     <t>Patient.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -1645,7 +1645,7 @@
     <t>contactIdentifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-contact-identifier}
 </t>
   </si>
   <si>
@@ -1661,7 +1661,7 @@
     <t>comment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-comment}
 </t>
   </si>
   <si>
@@ -1725,7 +1725,7 @@
     <t>The nature of the relationship. Rôle de la personne</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RolePerson.id</t>
@@ -1944,7 +1944,7 @@
     <t>The nature of the relationship. Relation de la personne</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelatedPerson.id</t>
@@ -2169,7 +2169,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
 </t>
   </si>
   <si>
@@ -2193,7 +2193,7 @@
     <t>Patient.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2586,7 +2586,7 @@
     <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="142.73046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="144.640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,7 +919,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
     &lt;display value="INS calculé"/&gt;
   &lt;/coding&gt;
@@ -1092,14 +1092,14 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
     &lt;display value="Identifiant au dossier pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-core-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.system</t>
@@ -2725,7 +2725,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.94140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.37109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -911,7 +911,7 @@
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
-    &lt;display value="INS calculé"/&gt;
+    &lt;display value="Identifiant National de Santé Calculé"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1084,7 +1084,7 @@
   &lt;coding&gt;
     &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
-    &lt;display value="Identifiant au dossier pharmaceutique"/&gt;
+    &lt;display value="Identifiant du patient au Dossier Pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4671" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4968" uniqueCount="676">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -828,33 +828,12 @@
     <t>PID-3</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C</t>
-  </si>
-  <si>
-    <t>INS-C</t>
-  </si>
-  <si>
-    <t>An identifier for this patient</t>
-  </si>
-  <si>
-    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
-  </si>
-  <si>
-    <t>Patient.identifier:INS-C.id</t>
-  </si>
-  <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.extension</t>
-  </si>
-  <si>
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Patient.identifier:INS-C.use</t>
-  </si>
-  <si>
     <t>Patient.identifier.use</t>
   </si>
   <si>
@@ -870,9 +849,6 @@
     <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
-    <t>secondary</t>
-  </si>
-  <si>
     <t>required</t>
   </si>
   <si>
@@ -886,9 +862,6 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Patient.identifier:INS-C.type</t>
   </si>
   <si>
     <t>Patient.identifier.type</t>
@@ -901,10 +874,159 @@
     <t>Description of identifier</t>
   </si>
   <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Patient.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>Patient.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>Patient.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C</t>
+  </si>
+  <si>
+    <t>INS-C</t>
+  </si>
+  <si>
+    <t>An identifier for this patient</t>
+  </si>
+  <si>
+    <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.use</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>Patient.identifier:INS-C.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -922,137 +1044,21 @@
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
-    <t>Patient.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
     <t>urn:oid:1.2.250.1.213.1.4.2</t>
   </si>
   <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.value</t>
   </si>
   <si>
-    <t>Patient.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.period</t>
   </si>
   <si>
-    <t>Patient.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.assigner</t>
   </si>
   <si>
-    <t>Patient.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
     <t>Patient.identifier:NDP</t>
   </si>
   <si>
@@ -1075,9 +1081,6 @@
   </si>
   <si>
     <t>Patient.identifier:NDP.type</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1087,9 +1090,6 @@
     &lt;display value="Identifiant du patient au Dossier Pharmaceutique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.system</t>
@@ -2449,7 +2449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO124"/>
+  <dimension ref="A1:AO132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.86328125" customWidth="true" bestFit="true"/>
@@ -5896,11 +5896,9 @@
         <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5909,7 +5907,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5918,21 +5916,19 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>262</v>
+        <v>106</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>263</v>
+        <v>107</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>81</v>
       </c>
@@ -5980,31 +5976,31 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -6012,21 +6008,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -6038,15 +6034,17 @@
         <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -6083,34 +6081,34 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>81</v>
@@ -6127,44 +6125,46 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
       </c>
@@ -6188,55 +6188,55 @@
         <v>81</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>119</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6264,25 +6264,25 @@
         <v>81</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>81</v>
@@ -6292,7 +6292,7 @@
         <v>81</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>274</v>
+        <v>81</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>81</v>
@@ -6307,13 +6307,11 @@
         <v>81</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>81</v>
@@ -6331,7 +6329,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6346,7 +6344,7 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
@@ -6355,7 +6353,7 @@
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6363,7 +6361,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>281</v>
@@ -6374,7 +6372,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
@@ -6389,13 +6387,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>284</v>
@@ -6411,11 +6409,11 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T34" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="T34" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="U34" t="s" s="2">
         <v>81</v>
       </c>
@@ -6426,31 +6424,31 @@
         <v>81</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6465,7 +6463,7 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
@@ -6474,7 +6472,7 @@
         <v>81</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6482,10 +6480,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6508,20 +6506,18 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -6530,10 +6526,10 @@
         <v>81</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>81</v>
@@ -6569,7 +6565,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6584,7 +6580,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -6593,7 +6589,7 @@
         <v>81</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6601,10 +6597,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6612,7 +6608,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
@@ -6627,16 +6623,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6650,7 +6646,7 @@
         <v>81</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>81</v>
@@ -6686,7 +6682,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6698,10 +6694,10 @@
         <v>101</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
@@ -6710,7 +6706,7 @@
         <v>81</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6718,10 +6714,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6744,16 +6740,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6803,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6815,10 +6811,10 @@
         <v>101</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>81</v>
@@ -6827,7 +6823,7 @@
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>81</v>
@@ -6835,12 +6831,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6849,7 +6847,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6861,18 +6859,18 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6920,31 +6918,31 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6952,14 +6950,12 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6977,21 +6973,19 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>106</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>107</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
       </c>
@@ -7039,31 +7033,31 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -7071,21 +7065,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -7097,15 +7091,17 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -7142,34 +7138,34 @@
         <v>81</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>81</v>
@@ -7186,44 +7182,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -7232,7 +7230,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -7247,55 +7245,55 @@
         <v>81</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>119</v>
+        <v>270</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7303,10 +7301,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7314,7 +7312,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
@@ -7323,25 +7321,25 @@
         <v>81</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -7351,7 +7349,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7366,13 +7364,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7390,7 +7388,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7405,7 +7403,7 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>81</v>
@@ -7414,7 +7412,7 @@
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>81</v>
@@ -7422,7 +7420,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>281</v>
@@ -7433,7 +7431,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -7448,13 +7446,13 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>284</v>
@@ -7470,10 +7468,10 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>81</v>
@@ -7485,11 +7483,13 @@
         <v>81</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>341</v>
+        <v>81</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -7507,7 +7507,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7522,7 +7522,7 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>81</v>
@@ -7531,7 +7531,7 @@
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7565,20 +7565,18 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7587,10 +7585,10 @@
         <v>81</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>81</v>
@@ -7626,7 +7624,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7641,7 +7639,7 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>81</v>
@@ -7650,7 +7648,7 @@
         <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7658,10 +7656,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7669,7 +7667,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -7684,16 +7682,16 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7707,7 +7705,7 @@
         <v>81</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>81</v>
@@ -7743,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7755,10 +7753,10 @@
         <v>101</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>81</v>
@@ -7767,7 +7765,7 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7775,10 +7773,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7801,16 +7799,16 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7860,7 +7858,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7872,10 +7870,10 @@
         <v>101</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>81</v>
@@ -7884,7 +7882,7 @@
         <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7892,12 +7890,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7918,18 +7918,18 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7977,31 +7977,31 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>81</v>
@@ -8009,14 +8009,12 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>81</v>
       </c>
@@ -8034,21 +8032,19 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>349</v>
+        <v>106</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -8096,31 +8092,31 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -8128,21 +8124,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -8154,15 +8150,17 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -8199,34 +8197,34 @@
         <v>81</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>81</v>
@@ -8243,44 +8241,46 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -8304,55 +8304,55 @@
         <v>81</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>119</v>
+        <v>270</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>81</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -8380,25 +8380,25 @@
         <v>81</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8408,7 +8408,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8423,13 +8423,11 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8447,7 +8445,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8462,7 +8460,7 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>81</v>
@@ -8471,7 +8469,7 @@
         <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>81</v>
@@ -8479,7 +8477,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>281</v>
@@ -8505,13 +8503,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>284</v>
@@ -8527,10 +8525,10 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>81</v>
@@ -8542,31 +8540,31 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8581,7 +8579,7 @@
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>81</v>
@@ -8590,7 +8588,7 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>81</v>
@@ -8598,10 +8596,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8624,20 +8622,18 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8649,7 +8645,7 @@
         <v>81</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>81</v>
@@ -8685,7 +8681,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8700,7 +8696,7 @@
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>81</v>
@@ -8709,7 +8705,7 @@
         <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>81</v>
@@ -8717,10 +8713,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8728,7 +8724,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>89</v>
@@ -8743,16 +8739,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8766,7 +8762,7 @@
         <v>81</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>81</v>
@@ -8802,7 +8798,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8814,10 +8810,10 @@
         <v>101</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>81</v>
@@ -8826,7 +8822,7 @@
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8834,10 +8830,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8860,16 +8856,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8919,7 +8915,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8931,10 +8927,10 @@
         <v>101</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>81</v>
@@ -8943,7 +8939,7 @@
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8951,12 +8947,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="D56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8977,18 +8975,18 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
       </c>
@@ -9036,31 +9034,31 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -9068,14 +9066,12 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>81</v>
       </c>
@@ -9093,21 +9089,19 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>250</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>362</v>
+        <v>106</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>107</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
       </c>
@@ -9155,31 +9149,31 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>249</v>
+        <v>108</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>257</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -9187,21 +9181,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>81</v>
@@ -9213,15 +9207,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -9258,34 +9254,34 @@
         <v>81</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>81</v>
@@ -9302,44 +9298,46 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9348,7 +9346,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9363,55 +9361,55 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>119</v>
+        <v>270</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9419,10 +9417,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9430,7 +9428,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>89</v>
@@ -9439,25 +9437,25 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9467,7 +9465,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>274</v>
+        <v>355</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -9482,13 +9480,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>275</v>
+        <v>153</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9506,7 +9504,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9521,7 +9519,7 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>81</v>
@@ -9530,7 +9528,7 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9538,7 +9536,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>281</v>
@@ -9564,13 +9562,13 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>284</v>
@@ -9586,10 +9584,10 @@
         <v>81</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="T61" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U61" t="s" s="2">
         <v>81</v>
@@ -9601,31 +9599,31 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9640,7 +9638,7 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>81</v>
@@ -9649,7 +9647,7 @@
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>81</v>
@@ -9657,10 +9655,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9683,20 +9681,18 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9708,7 +9704,7 @@
         <v>81</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>81</v>
@@ -9744,7 +9740,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9759,7 +9755,7 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>81</v>
@@ -9768,7 +9764,7 @@
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9776,10 +9772,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9787,7 +9783,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9802,16 +9798,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9825,7 +9821,7 @@
         <v>81</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>307</v>
+        <v>81</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>81</v>
@@ -9861,7 +9857,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9873,10 +9869,10 @@
         <v>101</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
@@ -9885,7 +9881,7 @@
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>81</v>
@@ -9893,10 +9889,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9919,16 +9915,16 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9978,7 +9974,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9990,10 +9986,10 @@
         <v>101</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>81</v>
@@ -10002,7 +9998,7 @@
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -10010,12 +10006,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>81</v>
       </c>
@@ -10036,18 +10034,18 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -10095,31 +10093,31 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>327</v>
+        <v>249</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>329</v>
+        <v>256</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -10127,10 +10125,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>372</v>
+        <v>260</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10147,32 +10145,26 @@
         <v>81</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>373</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>374</v>
+        <v>106</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q66" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10216,7 +10208,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>372</v>
+        <v>108</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10225,19 +10217,19 @@
         <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>379</v>
+        <v>109</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -10248,14 +10240,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>381</v>
+        <v>261</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10271,23 +10263,21 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>383</v>
+        <v>113</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>384</v>
+        <v>114</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10323,9 +10313,11 @@
         <v>81</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AC67" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10333,7 +10325,7 @@
         <v>118</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>381</v>
+        <v>119</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10345,19 +10337,19 @@
         <v>101</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>388</v>
+        <v>103</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>81</v>
@@ -10365,14 +10357,12 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>81</v>
       </c>
@@ -10381,31 +10371,31 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>393</v>
+        <v>173</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>394</v>
+        <v>263</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>264</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>385</v>
+        <v>265</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>386</v>
+        <v>266</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10415,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>81</v>
@@ -10430,13 +10420,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10454,13 +10444,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>381</v>
+        <v>270</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>101</v>
@@ -10469,16 +10459,16 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>388</v>
+        <v>271</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>390</v>
+        <v>103</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>81</v>
@@ -10486,10 +10476,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>397</v>
+        <v>272</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10497,7 +10487,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>89</v>
@@ -10509,19 +10499,23 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10530,7 +10524,7 @@
         <v>81</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>81</v>
+        <v>367</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>81</v>
@@ -10545,13 +10539,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>81</v>
+        <v>327</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10569,7 +10563,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10578,13 +10572,13 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>81</v>
@@ -10593,7 +10587,7 @@
         <v>81</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>81</v>
@@ -10601,21 +10595,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>281</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>
@@ -10624,21 +10618,23 @@
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>113</v>
+        <v>282</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>114</v>
+        <v>283</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
       </c>
@@ -10650,7 +10646,7 @@
         <v>81</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>81</v>
@@ -10674,34 +10670,34 @@
         <v>81</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>119</v>
+        <v>287</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>81</v>
@@ -10710,7 +10706,7 @@
         <v>81</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>81</v>
+        <v>289</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>81</v>
@@ -10718,10 +10714,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>401</v>
+        <v>290</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10738,26 +10734,24 @@
         <v>81</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>402</v>
+        <v>291</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>292</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
       </c>
@@ -10766,10 +10760,10 @@
         <v>81</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>81</v>
@@ -10781,13 +10775,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10805,7 +10799,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>408</v>
+        <v>295</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10820,7 +10814,7 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>409</v>
+        <v>296</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>81</v>
@@ -10829,7 +10823,7 @@
         <v>81</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10837,10 +10831,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>298</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10863,20 +10857,18 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>413</v>
+        <v>300</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>414</v>
+        <v>301</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10924,7 +10916,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>303</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10936,10 +10928,10 @@
         <v>101</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>418</v>
+        <v>305</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>81</v>
@@ -10948,7 +10940,7 @@
         <v>81</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>419</v>
+        <v>306</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>81</v>
@@ -10956,14 +10948,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>307</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10982,16 +10974,16 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>423</v>
+        <v>309</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>424</v>
+        <v>310</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>425</v>
+        <v>311</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11041,7 +11033,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>312</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11053,10 +11045,10 @@
         <v>101</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>427</v>
+        <v>314</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>81</v>
@@ -11065,7 +11057,7 @@
         <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>428</v>
+        <v>315</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>81</v>
@@ -11073,48 +11065,52 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>429</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>372</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>105</v>
+        <v>373</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>432</v>
+        <v>374</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>433</v>
+        <v>375</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" s="2"/>
+      <c r="Q74" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11158,13 +11154,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>101</v>
@@ -11173,16 +11169,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>436</v>
+        <v>379</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>81</v>
+        <v>380</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>437</v>
+        <v>81</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11190,10 +11186,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>381</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11216,18 +11212,20 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>105</v>
+        <v>382</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>440</v>
+        <v>383</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>441</v>
+        <v>384</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -11263,19 +11261,17 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>443</v>
+        <v>381</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11290,16 +11286,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>445</v>
+        <v>390</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11307,12 +11303,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11333,18 +11331,20 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>449</v>
+        <v>395</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>450</v>
+        <v>381</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11407,16 +11407,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>451</v>
+        <v>388</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11424,10 +11424,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>453</v>
+        <v>396</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
+        <v>397</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11447,23 +11447,19 @@
         <v>81</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>313</v>
+        <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>455</v>
+        <v>106</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11511,7 +11507,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>458</v>
+        <v>108</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11520,13 +11516,13 @@
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>459</v>
+        <v>109</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
@@ -11535,7 +11531,7 @@
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11543,16 +11539,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>461</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>462</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11568,23 +11562,21 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>393</v>
+        <v>112</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>463</v>
+        <v>113</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>464</v>
+        <v>114</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11620,19 +11612,19 @@
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>381</v>
+        <v>119</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11644,19 +11636,19 @@
         <v>101</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>388</v>
+        <v>103</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>390</v>
+        <v>81</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11664,10 +11656,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>465</v>
+        <v>400</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11675,7 +11667,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -11684,22 +11676,26 @@
         <v>81</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>106</v>
+        <v>402</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
@@ -11708,7 +11704,7 @@
         <v>81</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>81</v>
@@ -11723,13 +11719,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -11747,7 +11743,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>108</v>
+        <v>408</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11756,13 +11752,13 @@
         <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
@@ -11771,7 +11767,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11779,21 +11775,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>466</v>
+        <v>411</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
@@ -11802,21 +11798,23 @@
         <v>81</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>113</v>
+        <v>413</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>114</v>
+        <v>414</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11852,34 +11850,34 @@
         <v>81</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>119</v>
+        <v>417</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>103</v>
+        <v>418</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>81</v>
@@ -11888,7 +11886,7 @@
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11896,18 +11894,18 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
@@ -11916,26 +11914,24 @@
         <v>81</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>81</v>
       </c>
@@ -11944,7 +11940,7 @@
         <v>81</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>81</v>
@@ -11959,13 +11955,13 @@
         <v>81</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>81</v>
@@ -11983,7 +11979,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11998,7 +11994,7 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
@@ -12007,7 +12003,7 @@
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12015,21 +12011,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -12044,17 +12040,15 @@
         <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
       </c>
@@ -12102,13 +12096,13 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>101</v>
@@ -12117,7 +12111,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -12126,7 +12120,7 @@
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12134,21 +12128,21 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -12163,13 +12157,13 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12219,13 +12213,13 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>101</v>
@@ -12234,7 +12228,7 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>81</v>
@@ -12243,7 +12237,7 @@
         <v>81</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
@@ -12251,21 +12245,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>471</v>
+        <v>446</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>81</v>
@@ -12280,13 +12274,13 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12336,7 +12330,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12351,7 +12345,7 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>81</v>
@@ -12360,7 +12354,7 @@
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12368,10 +12362,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12382,7 +12376,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12394,18 +12388,20 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -12453,22 +12449,22 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>81</v>
@@ -12477,7 +12473,7 @@
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12485,12 +12481,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12511,18 +12509,20 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12570,7 +12570,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>450</v>
+        <v>381</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12585,16 +12585,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>451</v>
+        <v>388</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>452</v>
+        <v>390</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12602,10 +12602,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>397</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12625,23 +12625,19 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>313</v>
+        <v>105</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>455</v>
+        <v>106</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
       </c>
@@ -12689,7 +12685,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>458</v>
+        <v>108</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12698,13 +12694,13 @@
         <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>318</v>
+        <v>81</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>459</v>
+        <v>109</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>81</v>
@@ -12713,7 +12709,7 @@
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>460</v>
+        <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>81</v>
@@ -12721,14 +12717,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>475</v>
+        <v>399</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12747,20 +12743,18 @@
         <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>476</v>
+        <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>477</v>
+        <v>113</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>478</v>
+        <v>114</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12796,19 +12790,19 @@
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>475</v>
+        <v>119</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12820,10 +12814,10 @@
         <v>101</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>481</v>
+        <v>120</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>482</v>
+        <v>103</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>81</v>
@@ -12832,7 +12826,7 @@
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -12840,10 +12834,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>484</v>
+        <v>401</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12851,7 +12845,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>89</v>
@@ -12860,7 +12854,7 @@
         <v>81</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>90</v>
@@ -12869,16 +12863,16 @@
         <v>173</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>485</v>
+        <v>402</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>486</v>
+        <v>403</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>487</v>
+        <v>404</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>488</v>
+        <v>405</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12888,7 +12882,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>81</v>
+        <v>468</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12903,13 +12897,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>489</v>
+        <v>406</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>490</v>
+        <v>407</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12927,7 +12921,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>484</v>
+        <v>408</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12942,16 +12936,16 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>491</v>
+        <v>409</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>493</v>
+        <v>410</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -12959,10 +12953,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>494</v>
+        <v>412</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12985,19 +12979,19 @@
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>495</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>496</v>
+        <v>413</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>496</v>
+        <v>414</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>497</v>
+        <v>415</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>498</v>
+        <v>416</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13046,7 +13040,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>494</v>
+        <v>417</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13061,35 +13055,35 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>499</v>
+        <v>418</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>500</v>
+        <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>501</v>
+        <v>419</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>89</v>
@@ -13098,26 +13092,24 @@
         <v>81</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>504</v>
+        <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>505</v>
+        <v>423</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>506</v>
+        <v>424</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13165,7 +13157,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>503</v>
+        <v>426</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13180,16 +13172,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>509</v>
+        <v>427</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13197,21 +13189,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>511</v>
+        <v>471</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>511</v>
+        <v>430</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>81</v>
@@ -13220,23 +13212,21 @@
         <v>81</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>238</v>
+        <v>432</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>239</v>
+        <v>433</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
       </c>
@@ -13284,7 +13274,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>511</v>
+        <v>435</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13299,7 +13289,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>242</v>
+        <v>436</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
@@ -13308,7 +13298,7 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>243</v>
+        <v>437</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13316,10 +13306,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>513</v>
+        <v>472</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>513</v>
+        <v>439</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13330,7 +13320,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -13339,23 +13329,21 @@
         <v>81</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>282</v>
+        <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>514</v>
+        <v>440</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>515</v>
+        <v>441</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -13379,13 +13367,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -13403,13 +13391,13 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>513</v>
+        <v>443</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>101</v>
@@ -13418,16 +13406,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>520</v>
+        <v>444</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>521</v>
+        <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>522</v>
+        <v>445</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13435,10 +13423,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>523</v>
+        <v>473</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>523</v>
+        <v>447</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13449,7 +13437,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13458,23 +13446,21 @@
         <v>81</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>525</v>
+        <v>448</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>526</v>
+        <v>449</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -13522,13 +13508,13 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>523</v>
+        <v>450</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>101</v>
@@ -13537,16 +13523,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>529</v>
+        <v>451</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>530</v>
+        <v>452</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13554,10 +13540,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>454</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13568,7 +13554,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -13577,22 +13563,22 @@
         <v>81</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>532</v>
+        <v>299</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>533</v>
+        <v>455</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>534</v>
+        <v>456</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>535</v>
+        <v>302</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>536</v>
+        <v>457</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -13641,31 +13627,31 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>531</v>
+        <v>458</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>537</v>
+        <v>304</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>538</v>
+        <v>459</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>539</v>
+        <v>460</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13673,10 +13659,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13699,19 +13685,19 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>541</v>
+        <v>476</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>542</v>
+        <v>477</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>543</v>
+        <v>478</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>544</v>
+        <v>479</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>545</v>
+        <v>480</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13760,7 +13746,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>540</v>
+        <v>475</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13772,19 +13758,19 @@
         <v>101</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>546</v>
+        <v>481</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>547</v>
+        <v>482</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>81</v>
+        <v>483</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13792,10 +13778,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>548</v>
+        <v>484</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>548</v>
+        <v>484</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13815,19 +13801,23 @@
         <v>81</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>106</v>
+        <v>485</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13851,13 +13841,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>81</v>
+        <v>490</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13875,7 +13865,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>108</v>
+        <v>484</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13884,22 +13874,22 @@
         <v>89</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>109</v>
+        <v>491</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>81</v>
+        <v>492</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13907,21 +13897,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>494</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>494</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>81</v>
@@ -13930,21 +13920,23 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>112</v>
+        <v>495</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>113</v>
+        <v>496</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>114</v>
+        <v>496</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13980,58 +13972,56 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>119</v>
+        <v>494</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>103</v>
+        <v>499</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>503</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14046,22 +14036,26 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>553</v>
+        <v>505</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
       </c>
@@ -14109,31 +14103,31 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>119</v>
+        <v>503</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>81</v>
@@ -14141,14 +14135,12 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14157,7 +14149,7 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -14169,16 +14161,20 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>557</v>
+        <v>237</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>558</v>
+        <v>238</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
       </c>
@@ -14226,7 +14222,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>119</v>
+        <v>511</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14238,10 +14234,10 @@
         <v>101</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>81</v>
@@ -14250,7 +14246,7 @@
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14258,45 +14254,45 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>560</v>
+        <v>513</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>560</v>
+        <v>513</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>562</v>
+        <v>514</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>563</v>
+        <v>515</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>115</v>
+        <v>516</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>247</v>
+        <v>517</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14321,13 +14317,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -14345,31 +14341,31 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>564</v>
+        <v>513</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>81</v>
+        <v>522</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14377,10 +14373,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14388,7 +14384,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -14403,19 +14399,19 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>282</v>
+        <v>524</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>566</v>
+        <v>525</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>567</v>
+        <v>526</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>568</v>
+        <v>528</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14440,35 +14436,37 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>570</v>
+        <v>81</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AC102" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>101</v>
@@ -14477,7 +14475,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>572</v>
+        <v>529</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>109</v>
@@ -14486,7 +14484,7 @@
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>573</v>
+        <v>530</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14494,14 +14492,12 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>574</v>
+        <v>531</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14510,7 +14506,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14522,19 +14518,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>282</v>
+        <v>532</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>576</v>
+        <v>533</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14559,11 +14555,13 @@
         <v>81</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>577</v>
+        <v>81</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>81</v>
@@ -14581,7 +14579,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>565</v>
+        <v>531</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14593,10 +14591,10 @@
         <v>101</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>537</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>572</v>
+        <v>538</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>109</v>
@@ -14605,7 +14603,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>573</v>
+        <v>539</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14613,14 +14611,12 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>578</v>
+        <v>540</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14629,7 +14625,7 @@
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>81</v>
@@ -14641,19 +14637,19 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>282</v>
+        <v>541</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>567</v>
+        <v>543</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>568</v>
+        <v>545</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14678,11 +14674,13 @@
         <v>81</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>581</v>
+        <v>81</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>81</v>
@@ -14700,7 +14698,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>565</v>
+        <v>540</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14712,10 +14710,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>102</v>
+        <v>546</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>572</v>
+        <v>547</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14724,7 +14722,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>573</v>
+        <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14732,10 +14730,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14758,20 +14756,16 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>382</v>
+        <v>105</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>583</v>
+        <v>106</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14819,7 +14813,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>582</v>
+        <v>108</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14828,13 +14822,13 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>587</v>
+        <v>109</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>81</v>
@@ -14843,7 +14837,7 @@
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>588</v>
+        <v>81</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>81</v>
@@ -14851,14 +14845,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>589</v>
+        <v>549</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>589</v>
+        <v>549</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14877,20 +14871,18 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>476</v>
+        <v>112</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>477</v>
+        <v>113</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>478</v>
+        <v>114</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
       </c>
@@ -14926,19 +14918,19 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>589</v>
+        <v>119</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14950,10 +14942,10 @@
         <v>101</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>481</v>
+        <v>120</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>482</v>
+        <v>103</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>81</v>
@@ -14962,7 +14954,7 @@
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -14970,12 +14962,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>550</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>81</v>
       </c>
@@ -14996,20 +14990,16 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>592</v>
+        <v>552</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>593</v>
+        <v>553</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15057,31 +15047,31 @@
         <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>119</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>596</v>
+        <v>81</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>597</v>
+        <v>81</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -15089,12 +15079,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>598</v>
+        <v>555</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15115,20 +15107,16 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>173</v>
+        <v>557</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>485</v>
+        <v>558</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15152,13 +15140,13 @@
         <v>81</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>81</v>
@@ -15176,31 +15164,31 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>598</v>
+        <v>119</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>491</v>
+        <v>81</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>601</v>
+        <v>81</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>81</v>
@@ -15208,45 +15196,45 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>602</v>
+        <v>560</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>602</v>
+        <v>560</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>81</v>
+        <v>561</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>323</v>
+        <v>112</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>603</v>
+        <v>562</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>604</v>
+        <v>563</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>605</v>
+        <v>115</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>606</v>
+        <v>247</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15295,31 +15283,31 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>602</v>
+        <v>564</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>607</v>
+        <v>101</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>328</v>
+        <v>120</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>608</v>
+        <v>103</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>609</v>
+        <v>81</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15327,10 +15315,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15338,7 +15326,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>89</v>
@@ -15353,18 +15341,20 @@
         <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>611</v>
+        <v>566</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>612</v>
+        <v>567</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
       </c>
@@ -15388,46 +15378,44 @@
         <v>81</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>81</v>
+        <v>569</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>81</v>
+        <v>570</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>318</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>613</v>
+        <v>572</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>109</v>
@@ -15436,7 +15424,7 @@
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>614</v>
+        <v>573</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15444,12 +15432,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>615</v>
+        <v>574</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15458,7 +15448,7 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>81</v>
@@ -15470,19 +15460,19 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>541</v>
+        <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>617</v>
+        <v>567</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>618</v>
+        <v>516</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>619</v>
+        <v>568</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15507,13 +15497,11 @@
         <v>81</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>81</v>
+        <v>577</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15531,7 +15519,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>615</v>
+        <v>565</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15546,16 +15534,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>620</v>
+        <v>572</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>621</v>
+        <v>109</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15563,12 +15551,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>622</v>
+        <v>578</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C112" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15589,16 +15579,20 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>106</v>
+        <v>580</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15622,13 +15616,11 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>81</v>
+        <v>581</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15646,31 +15638,31 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>108</v>
+        <v>565</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AL112" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15678,21 +15670,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>623</v>
+        <v>582</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>623</v>
+        <v>582</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15704,18 +15696,20 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>112</v>
+        <v>382</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>113</v>
+        <v>583</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>114</v>
+        <v>584</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15751,34 +15745,34 @@
         <v>81</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>119</v>
+        <v>582</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>103</v>
+        <v>587</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>81</v>
@@ -15787,7 +15781,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15795,14 +15789,14 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>624</v>
+        <v>589</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>624</v>
+        <v>589</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15815,25 +15809,25 @@
         <v>81</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>112</v>
+        <v>476</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>562</v>
+        <v>477</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>563</v>
+        <v>478</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>115</v>
+        <v>590</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>247</v>
+        <v>480</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15882,7 +15876,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15894,10 +15888,10 @@
         <v>101</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>120</v>
+        <v>481</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>103</v>
+        <v>482</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>81</v>
@@ -15906,7 +15900,7 @@
         <v>81</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>81</v>
+        <v>483</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15914,10 +15908,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>625</v>
+        <v>591</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>625</v>
+        <v>591</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15925,7 +15919,7 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>89</v>
@@ -15940,19 +15934,19 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>282</v>
+        <v>592</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>626</v>
+        <v>593</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>627</v>
+        <v>594</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>628</v>
+        <v>240</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>629</v>
+        <v>595</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -15977,13 +15971,13 @@
         <v>81</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>81</v>
@@ -16001,10 +15995,10 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>625</v>
+        <v>591</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>89</v>
@@ -16016,16 +16010,16 @@
         <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>630</v>
+        <v>596</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>631</v>
+        <v>109</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>632</v>
+        <v>597</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16033,10 +16027,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>633</v>
+        <v>598</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>633</v>
+        <v>598</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16059,19 +16053,19 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>373</v>
+        <v>173</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>634</v>
+        <v>485</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>636</v>
+        <v>442</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>637</v>
+        <v>600</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16096,13 +16090,13 @@
         <v>81</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>81</v>
+        <v>489</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>81</v>
+        <v>490</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>81</v>
@@ -16120,7 +16114,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>633</v>
+        <v>598</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16135,16 +16129,16 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>638</v>
+        <v>491</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>639</v>
+        <v>109</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>640</v>
+        <v>601</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16152,21 +16146,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>642</v>
+        <v>81</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>81</v>
@@ -16178,18 +16172,20 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>643</v>
+        <v>308</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>644</v>
+        <v>603</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16237,22 +16233,22 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>641</v>
+        <v>602</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>101</v>
+        <v>607</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>647</v>
+        <v>608</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>109</v>
@@ -16261,7 +16257,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>648</v>
+        <v>609</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16269,10 +16265,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>649</v>
+        <v>610</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>649</v>
+        <v>610</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16292,23 +16288,21 @@
         <v>81</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>650</v>
+        <v>299</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>651</v>
+        <v>611</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>652</v>
+        <v>612</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>654</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16356,7 +16350,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>649</v>
+        <v>610</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16368,19 +16362,19 @@
         <v>101</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>655</v>
+        <v>109</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>81</v>
+        <v>614</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16388,10 +16382,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16408,25 +16402,25 @@
         <v>81</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>541</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>657</v>
+        <v>616</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>658</v>
+        <v>617</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>659</v>
+        <v>618</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>660</v>
+        <v>619</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -16475,7 +16469,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16490,10 +16484,10 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>661</v>
+        <v>620</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>109</v>
+        <v>621</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
@@ -16507,10 +16501,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>662</v>
+        <v>622</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16622,10 +16616,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>663</v>
+        <v>623</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16739,10 +16733,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>664</v>
+        <v>624</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>664</v>
+        <v>624</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16858,10 +16852,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16881,21 +16875,23 @@
         <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>666</v>
+        <v>273</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>667</v>
+        <v>626</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>668</v>
+        <v>627</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O123" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
       </c>
@@ -16919,13 +16915,13 @@
         <v>81</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>81</v>
@@ -16943,7 +16939,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>665</v>
+        <v>625</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>89</v>
@@ -16955,19 +16951,19 @@
         <v>101</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>328</v>
+        <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>256</v>
+        <v>630</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>109</v>
+        <v>631</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>670</v>
+        <v>632</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -16975,10 +16971,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>671</v>
+        <v>633</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>671</v>
+        <v>633</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16986,7 +16982,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>89</v>
@@ -16998,21 +16994,23 @@
         <v>81</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>173</v>
+        <v>373</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>672</v>
+        <v>634</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>673</v>
+        <v>635</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
       </c>
@@ -17036,13 +17034,13 @@
         <v>81</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>673</v>
+        <v>81</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>674</v>
+        <v>81</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>81</v>
@@ -17060,10 +17058,10 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>671</v>
+        <v>633</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>89</v>
@@ -17075,18 +17073,958 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK132" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AL132" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AM124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO124" t="s" s="2">
+      <c r="AM132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO132" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4968" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1486,6 +1486,22 @@
   </si>
   <si>
     <t>Patient.name:officialName.extension</t>
+  </si>
+  <si>
+    <t>Patient.name:officialName.extension:birth-list-given-name</t>
+  </si>
+  <si>
+    <t>birth-list-given-name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-birth-list-given-name}
+</t>
+  </si>
+  <si>
+    <t>Dans le cas d’une identité créée ou modifiée par un appel au téléservice INSi, il s’agit de la liste des prénoms retournée par le téléservice. Ce composant contient tous les prénoms du patient, y compris le premier, que l'on retrouve également dans le champ name.given. Il s'agit de la liste des prénoms du patient, qu'elle soit issue d'une saisie locale ou du retour à l'appel au téléservice INSi. Conformément aux spécifications INS, cette liste est constituée des prénoms, séparés par des espaces.</t>
+  </si>
+  <si>
+    <t>Prénoms de l'acte de naissance</t>
   </si>
   <si>
     <t>Patient.name:officialName.use</t>
@@ -2449,10 +2465,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO132"/>
+  <dimension ref="A1:AO133"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.86328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="39.47265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.2265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -12837,15 +12853,17 @@
         <v>467</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>89</v>
@@ -12854,26 +12872,22 @@
         <v>81</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>173</v>
+        <v>469</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>402</v>
+        <v>470</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12882,7 +12896,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>468</v>
+        <v>81</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12897,13 +12911,13 @@
         <v>81</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
@@ -12921,22 +12935,22 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>408</v>
+        <v>119</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
@@ -12945,7 +12959,7 @@
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -12953,10 +12967,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12964,7 +12978,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12973,25 +12987,25 @@
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13001,7 +13015,7 @@
         <v>81</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>81</v>
@@ -13016,13 +13030,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13040,7 +13054,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13055,7 +13069,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>81</v>
@@ -13064,7 +13078,7 @@
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13072,18 +13086,18 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>89</v>
@@ -13101,15 +13115,17 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13157,7 +13173,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13172,7 +13188,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
@@ -13181,7 +13197,7 @@
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13189,14 +13205,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13218,13 +13234,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13274,13 +13290,13 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>101</v>
@@ -13289,7 +13305,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
@@ -13298,7 +13314,7 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13306,21 +13322,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -13335,13 +13351,13 @@
         <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13391,7 +13407,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13406,7 +13422,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
@@ -13415,7 +13431,7 @@
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13423,10 +13439,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13452,10 +13468,10 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>442</v>
@@ -13508,7 +13524,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13523,7 +13539,7 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>81</v>
@@ -13532,7 +13548,7 @@
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13540,10 +13556,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13554,7 +13570,7 @@
         <v>79</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -13566,20 +13582,18 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13627,22 +13641,22 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>81</v>
@@ -13651,7 +13665,7 @@
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13659,10 +13673,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13673,7 +13687,7 @@
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>81</v>
@@ -13682,22 +13696,22 @@
         <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>476</v>
+        <v>299</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>479</v>
+        <v>302</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13746,22 +13760,22 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>481</v>
+        <v>304</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>81</v>
@@ -13770,7 +13784,7 @@
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>483</v>
+        <v>460</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13778,10 +13792,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13792,7 +13806,7 @@
         <v>79</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>81</v>
@@ -13801,22 +13815,22 @@
         <v>81</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>173</v>
+        <v>481</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O97" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13841,13 +13855,13 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13865,31 +13879,31 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13897,10 +13911,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13923,19 +13937,19 @@
         <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>495</v>
+        <v>173</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13960,13 +13974,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>81</v>
+        <v>495</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -13984,7 +13998,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13999,27 +14013,27 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>502</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14036,25 +14050,25 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14103,7 +14117,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14118,27 +14132,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>109</v>
+        <v>505</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>81</v>
+        <v>507</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14149,31 +14163,31 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>237</v>
+        <v>509</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>238</v>
+        <v>510</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>239</v>
+        <v>511</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>240</v>
+        <v>512</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14222,13 +14236,13 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>101</v>
@@ -14237,16 +14251,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>242</v>
+        <v>514</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>243</v>
+        <v>515</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14254,10 +14268,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14268,7 +14282,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14280,16 +14294,16 @@
         <v>81</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>514</v>
+        <v>238</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>515</v>
+        <v>239</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>516</v>
+        <v>240</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>517</v>
@@ -14317,13 +14331,13 @@
         <v>81</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>519</v>
+        <v>81</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>81</v>
@@ -14341,13 +14355,13 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>101</v>
@@ -14356,16 +14370,16 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>520</v>
+        <v>242</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>521</v>
+        <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>522</v>
+        <v>243</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14373,10 +14387,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14399,19 +14413,19 @@
         <v>81</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>524</v>
+        <v>273</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14436,13 +14450,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>81</v>
+        <v>523</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>81</v>
+        <v>524</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14460,7 +14474,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14475,16 +14489,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>109</v>
+        <v>526</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14492,10 +14506,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14506,7 +14520,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14518,19 +14532,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14579,22 +14593,22 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>537</v>
+        <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>109</v>
@@ -14603,7 +14617,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14611,10 +14625,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14637,19 +14651,19 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14698,7 +14712,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14710,10 +14724,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14722,7 +14736,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14730,10 +14744,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14744,7 +14758,7 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14756,16 +14770,20 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>105</v>
+        <v>546</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>106</v>
+        <v>547</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
       </c>
@@ -14813,25 +14831,25 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>108</v>
+        <v>545</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>81</v>
+        <v>551</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
@@ -14845,21 +14863,21 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14871,17 +14889,15 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>81</v>
@@ -14918,34 +14934,34 @@
         <v>81</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>81</v>
@@ -14962,23 +14978,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>81</v>
@@ -14990,15 +15004,17 @@
         <v>81</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>552</v>
+        <v>112</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>553</v>
+        <v>113</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -15035,16 +15051,16 @@
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>119</v>
@@ -15062,7 +15078,7 @@
         <v>120</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>81</v>
@@ -15082,7 +15098,7 @@
         <v>555</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>556</v>
@@ -15199,43 +15215,41 @@
         <v>560</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="C109" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="D109" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>112</v>
+        <v>562</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15283,7 +15297,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>564</v>
+        <v>119</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15298,7 +15312,7 @@
         <v>120</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>81</v>
@@ -15322,38 +15336,38 @@
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>516</v>
+        <v>115</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>568</v>
+        <v>247</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15378,29 +15392,31 @@
         <v>81</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AC110" s="2"/>
-      <c r="AD110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15412,19 +15428,19 @@
         <v>101</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>572</v>
+        <v>103</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>573</v>
+        <v>81</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15432,20 +15448,18 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>89</v>
@@ -15463,16 +15477,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15499,27 +15513,27 @@
       <c r="X111" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y111" s="2"/>
+      <c r="Y111" t="s" s="2">
+        <v>574</v>
+      </c>
       <c r="Z111" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15534,7 +15548,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>109</v>
@@ -15543,7 +15557,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15551,13 +15565,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -15582,16 +15596,16 @@
         <v>273</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15620,7 +15634,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15638,7 +15652,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15653,7 +15667,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15662,7 +15676,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15670,12 +15684,14 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15696,19 +15712,19 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>382</v>
+        <v>273</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>585</v>
+        <v>521</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15733,13 +15749,11 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>81</v>
+        <v>586</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15757,13 +15771,13 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>101</v>
@@ -15772,16 +15786,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15789,10 +15803,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15803,7 +15817,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>81</v>
@@ -15815,19 +15829,19 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>476</v>
+        <v>382</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>477</v>
+        <v>588</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>478</v>
+        <v>589</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>590</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>480</v>
+        <v>591</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15876,22 +15890,22 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>481</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>482</v>
+        <v>592</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>81</v>
@@ -15900,7 +15914,7 @@
         <v>81</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>483</v>
+        <v>593</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15908,10 +15922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15922,7 +15936,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
@@ -15934,19 +15948,19 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>592</v>
+        <v>481</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>593</v>
+        <v>482</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>594</v>
+        <v>483</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>240</v>
+        <v>595</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>595</v>
+        <v>485</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -15995,31 +16009,31 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>102</v>
+        <v>486</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>596</v>
+        <v>487</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>597</v>
+        <v>488</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16027,10 +16041,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16053,16 +16067,16 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>173</v>
+        <v>597</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>485</v>
+        <v>598</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>599</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>442</v>
+        <v>240</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>600</v>
@@ -16090,13 +16104,13 @@
         <v>81</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>489</v>
+        <v>81</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>490</v>
+        <v>81</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>81</v>
@@ -16114,7 +16128,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16129,7 +16143,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>491</v>
+        <v>601</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>109</v>
@@ -16138,7 +16152,7 @@
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16146,10 +16160,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16172,19 +16186,19 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>308</v>
+        <v>173</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>603</v>
+        <v>490</v>
       </c>
       <c r="M117" t="s" s="2">
         <v>604</v>
       </c>
       <c r="N117" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O117" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16209,13 +16223,13 @@
         <v>81</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>81</v>
+        <v>494</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>81</v>
+        <v>495</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -16233,7 +16247,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16242,13 +16256,13 @@
         <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>607</v>
+        <v>101</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>608</v>
+        <v>496</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>109</v>
@@ -16257,7 +16271,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16265,10 +16279,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16291,18 +16305,20 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O118" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M118" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16350,7 +16366,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16359,10 +16375,10 @@
         <v>89</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>101</v>
+        <v>612</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>613</v>
@@ -16396,7 +16412,7 @@
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
@@ -16408,7 +16424,7 @@
         <v>81</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>541</v>
+        <v>299</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>616</v>
@@ -16417,11 +16433,9 @@
         <v>617</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>81</v>
       </c>
@@ -16475,25 +16489,25 @@
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>621</v>
+        <v>109</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>81</v>
+        <v>619</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16501,10 +16515,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16515,7 +16529,7 @@
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>81</v>
@@ -16527,16 +16541,20 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>105</v>
+        <v>546</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>106</v>
+        <v>621</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
       </c>
@@ -16584,25 +16602,25 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>108</v>
+        <v>620</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>109</v>
+        <v>625</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>81</v>
+        <v>626</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16616,21 +16634,21 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>81</v>
@@ -16642,17 +16660,15 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16689,34 +16705,34 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>81</v>
@@ -16733,14 +16749,14 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>561</v>
+        <v>111</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16753,26 +16769,24 @@
         <v>81</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>562</v>
+        <v>113</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>563</v>
+        <v>114</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O122" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16808,19 +16822,19 @@
         <v>81</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>564</v>
+        <v>119</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16852,45 +16866,45 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>273</v>
+        <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>626</v>
+        <v>567</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>627</v>
+        <v>568</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>628</v>
+        <v>115</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>629</v>
+        <v>247</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16915,13 +16929,13 @@
         <v>81</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>81</v>
@@ -16939,31 +16953,31 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>625</v>
+        <v>569</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>630</v>
+        <v>103</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>631</v>
+        <v>81</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>632</v>
+        <v>81</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -16971,10 +16985,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16982,7 +16996,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>89</v>
@@ -16997,19 +17011,19 @@
         <v>81</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>373</v>
+        <v>273</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O124" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17034,13 +17048,13 @@
         <v>81</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>81</v>
+        <v>178</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>81</v>
@@ -17058,10 +17072,10 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>89</v>
@@ -17073,16 +17087,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17090,21 +17104,21 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>642</v>
+        <v>81</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>81</v>
@@ -17116,18 +17130,20 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>643</v>
+        <v>373</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>641</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>642</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
       </c>
@@ -17175,31 +17191,31 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>109</v>
+        <v>644</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17207,21 +17223,21 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>81</v>
+        <v>647</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17230,23 +17246,21 @@
         <v>81</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="M126" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>654</v>
-      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17294,13 +17308,13 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>101</v>
@@ -17309,16 +17323,16 @@
         <v>313</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>655</v>
+        <v>109</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>81</v>
+        <v>653</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17326,10 +17340,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17340,31 +17354,31 @@
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>541</v>
+        <v>655</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17413,25 +17427,25 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>661</v>
+        <v>613</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>109</v>
+        <v>660</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
@@ -17445,10 +17459,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17459,28 +17473,32 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>105</v>
+        <v>546</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>106</v>
+        <v>662</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>663</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>665</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17528,25 +17546,25 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>108</v>
+        <v>661</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AL128" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>81</v>
@@ -17560,21 +17578,21 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>81</v>
@@ -17586,17 +17604,15 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>81</v>
@@ -17633,34 +17649,34 @@
         <v>81</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>81</v>
@@ -17677,14 +17693,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>561</v>
+        <v>111</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17697,26 +17713,24 @@
         <v>81</v>
       </c>
       <c r="I130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>562</v>
+        <v>113</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>563</v>
+        <v>114</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O130" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
       </c>
@@ -17752,19 +17766,19 @@
         <v>81</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>564</v>
+        <v>119</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17796,44 +17810,46 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>81</v>
+        <v>566</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>666</v>
+        <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>667</v>
+        <v>567</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>668</v>
+        <v>568</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
       </c>
@@ -17881,31 +17897,31 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>665</v>
+        <v>569</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>313</v>
+        <v>120</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>670</v>
+        <v>81</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>81</v>
@@ -17913,10 +17929,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17939,7 +17955,7 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>173</v>
+        <v>671</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>672</v>
@@ -17948,7 +17964,7 @@
         <v>673</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>442</v>
+        <v>674</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -17974,13 +17990,13 @@
         <v>81</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>673</v>
+        <v>81</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>674</v>
+        <v>81</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>81</v>
@@ -17998,7 +18014,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>89</v>
@@ -18010,10 +18026,10 @@
         <v>101</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>675</v>
+        <v>256</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>109</v>
@@ -18022,9 +18038,126 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>81</v>
+        <v>675</v>
       </c>
       <c r="AO132" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO133" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -800,7 +800,7 @@
 </t>
   </si>
   <si>
-    <t>National Health Identifier | Identifiant national de santé</t>
+    <t>An identifier for this patient | Identifiant patient. Pour modéliser un patient avec une INS validée, il est nécessaire de respecter la conformité au profil FrCorePatientINS. Les identifiants NIR et NIA ne sont définis uniquement dans le cas du FRCorePatientINS.</t>
   </si>
   <si>
     <t>An identifier for this patient.</t>
@@ -4755,7 +4755,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -7922,7 +7922,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -10038,7 +10038,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1661,10 +1661,7 @@
     <t>Most, if not all systems capture it.</t>
   </si>
   <si>
-    <t>The domestic partnership status of a person.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-marital-status</t>
   </si>
   <si>
     <t>player[classCode=PSN]/maritalStatusCode</t>
@@ -14452,11 +14449,9 @@
       <c r="X102" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y102" t="s" s="2">
+      <c r="Y102" s="2"/>
+      <c r="Z102" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14489,16 +14484,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14506,10 +14501,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14532,19 +14527,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14593,7 +14588,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14608,7 +14603,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>109</v>
@@ -14617,7 +14612,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14625,10 +14620,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14651,19 +14646,19 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14712,7 +14707,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14724,10 +14719,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AK104" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14736,7 +14731,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14744,10 +14739,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14770,19 +14765,19 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14831,7 +14826,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14843,10 +14838,10 @@
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AK105" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>109</v>
@@ -14863,10 +14858,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14978,10 +14973,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15095,13 +15090,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
@@ -15123,13 +15118,13 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15212,13 +15207,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>81</v>
@@ -15240,13 +15235,13 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15329,14 +15324,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15358,10 +15353,10 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>115</v>
@@ -15416,7 +15411,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15448,10 +15443,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15477,16 +15472,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15514,16 +15509,16 @@
         <v>153</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z111" t="s" s="2">
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
@@ -15533,7 +15528,7 @@
         <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15548,7 +15543,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>109</v>
@@ -15557,7 +15552,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15565,13 +15560,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -15596,16 +15591,16 @@
         <v>273</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15634,7 +15629,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15652,7 +15647,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15667,7 +15662,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15676,7 +15671,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15684,13 +15679,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>81</v>
@@ -15715,16 +15710,16 @@
         <v>273</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>521</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15753,7 +15748,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15771,7 +15766,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15786,7 +15781,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15795,7 +15790,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15803,10 +15798,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15832,16 +15827,16 @@
         <v>382</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15890,7 +15885,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15905,16 +15900,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15922,10 +15917,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15957,7 +15952,7 @@
         <v>483</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>485</v>
@@ -16009,7 +16004,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16041,10 +16036,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16067,19 +16062,19 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>240</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16128,7 +16123,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16143,7 +16138,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>109</v>
@@ -16152,7 +16147,7 @@
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16160,10 +16155,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16192,13 +16187,13 @@
         <v>490</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16247,7 +16242,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16271,7 +16266,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16279,10 +16274,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16308,16 +16303,16 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16366,7 +16361,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16375,13 +16370,13 @@
         <v>89</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>109</v>
@@ -16390,7 +16385,7 @@
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16398,10 +16393,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16427,10 +16422,10 @@
         <v>299</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>616</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>302</v>
@@ -16483,7 +16478,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16498,7 +16493,7 @@
         <v>304</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>109</v>
@@ -16507,7 +16502,7 @@
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16515,10 +16510,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16541,19 +16536,19 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16602,7 +16597,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16617,10 +16612,10 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16634,10 +16629,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16749,10 +16744,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16866,14 +16861,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16895,10 +16890,10 @@
         <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>115</v>
@@ -16953,7 +16948,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16985,10 +16980,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17014,16 +17009,16 @@
         <v>273</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17072,7 +17067,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>89</v>
@@ -17087,16 +17082,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AM124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17104,10 +17099,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17133,16 +17128,16 @@
         <v>373</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>640</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17191,7 +17186,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17206,16 +17201,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17223,14 +17218,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17249,16 +17244,16 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17308,7 +17303,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17323,7 +17318,7 @@
         <v>313</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
@@ -17332,7 +17327,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17340,10 +17335,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17366,19 +17361,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>658</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17427,7 +17422,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17442,10 +17437,10 @@
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
@@ -17459,10 +17454,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17485,19 +17480,19 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17546,7 +17541,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17561,7 +17556,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17578,10 +17573,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17693,10 +17688,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17810,14 +17805,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17839,10 +17834,10 @@
         <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>115</v>
@@ -17897,7 +17892,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17929,10 +17924,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17955,16 +17950,16 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18014,7 +18009,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>89</v>
@@ -18038,7 +18033,7 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18046,10 +18041,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18075,10 +18070,10 @@
         <v>173</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>442</v>
@@ -18110,11 +18105,11 @@
         <v>267</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>679</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18131,7 +18126,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18146,7 +18141,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>109</v>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1065,10 +1065,7 @@
     <t>NDP</t>
   </si>
   <si>
-    <t>French pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique français</t>
-  </si>
-  <si>
-    <t>Pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique</t>
+    <t>French pharmaceutical Record Identifier | Numéro de Dossier Pharmaceutique français. Celui-ci est unique.</t>
   </si>
   <si>
     <t>Patient.identifier:NDP.id</t>
@@ -7919,7 +7916,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7937,7 +7934,7 @@
         <v>335</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>252</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -8022,7 +8019,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>260</v>
@@ -8137,7 +8134,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8254,7 +8251,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>262</v>
@@ -8373,7 +8370,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>272</v>
@@ -8421,7 +8418,7 @@
         <v>81</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>81</v>
@@ -8490,7 +8487,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>281</v>
@@ -8538,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>286</v>
@@ -8609,7 +8606,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>290</v>
@@ -8726,7 +8723,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>298</v>
@@ -8843,7 +8840,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>307</v>
@@ -8960,13 +8957,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>81</v>
@@ -8991,10 +8988,10 @@
         <v>250</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -9079,7 +9076,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>260</v>
@@ -9194,7 +9191,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>261</v>
@@ -9311,7 +9308,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>262</v>
@@ -9359,7 +9356,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9430,7 +9427,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>272</v>
@@ -9478,7 +9475,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -9549,7 +9546,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>281</v>
@@ -9668,7 +9665,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>290</v>
@@ -9785,7 +9782,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>298</v>
@@ -9902,7 +9899,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>307</v>
@@ -10019,13 +10016,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>81</v>
@@ -10050,10 +10047,10 @@
         <v>250</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -10138,7 +10135,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>260</v>
@@ -10253,7 +10250,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>261</v>
@@ -10370,7 +10367,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>262</v>
@@ -10489,7 +10486,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>272</v>
@@ -10537,7 +10534,7 @@
         <v>81</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>81</v>
@@ -10608,7 +10605,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>281</v>
@@ -10727,7 +10724,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>290</v>
@@ -10844,7 +10841,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>298</v>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>307</v>
@@ -11078,10 +11075,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11104,26 +11101,26 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="O74" t="s" s="2">
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="P74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q74" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11167,7 +11164,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11182,13 +11179,13 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11199,10 +11196,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11225,19 +11222,19 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>81</v>
@@ -11274,7 +11271,7 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11284,7 +11281,7 @@
         <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11299,16 +11296,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11316,13 +11313,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>81</v>
@@ -11344,19 +11341,19 @@
         <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="N76" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O76" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11405,7 +11402,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11420,16 +11417,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL76" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL76" t="s" s="2">
+      <c r="AM76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11437,10 +11434,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11552,10 +11549,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11669,10 +11666,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11698,16 +11695,16 @@
         <v>173</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11717,7 +11714,7 @@
         <v>81</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>81</v>
@@ -11735,28 +11732,28 @@
         <v>267</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z79" t="s" s="2">
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11771,16 +11768,16 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN79" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11788,10 +11785,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11817,16 +11814,16 @@
         <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>81</v>
@@ -11875,7 +11872,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11890,16 +11887,16 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11907,14 +11904,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11936,13 +11933,13 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11992,7 +11989,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12007,16 +12004,16 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12024,14 +12021,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12053,13 +12050,13 @@
         <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12109,7 +12106,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12124,16 +12121,16 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12141,10 +12138,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12170,13 +12167,13 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12226,7 +12223,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12241,16 +12238,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
@@ -12258,10 +12255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B84" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12287,13 +12284,13 @@
         <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="N84" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12343,7 +12340,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12358,16 +12355,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12375,10 +12372,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B85" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12404,16 +12401,16 @@
         <v>299</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>302</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12462,7 +12459,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12477,16 +12474,16 @@
         <v>304</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12494,13 +12491,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>81</v>
@@ -12522,19 +12519,19 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="N86" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O86" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -12583,7 +12580,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12598,16 +12595,16 @@
         <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL86" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12615,10 +12612,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12730,10 +12727,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12847,13 +12844,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>81</v>
@@ -12875,13 +12872,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12964,10 +12961,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12993,16 +12990,16 @@
         <v>173</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13012,7 +13009,7 @@
         <v>81</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>81</v>
@@ -13030,28 +13027,28 @@
         <v>267</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z90" t="s" s="2">
+      <c r="AA90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13066,16 +13063,16 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13083,10 +13080,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13112,16 +13109,16 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13170,7 +13167,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13185,16 +13182,16 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13202,14 +13199,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13231,13 +13228,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13287,7 +13284,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13302,16 +13299,16 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13319,14 +13316,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13348,13 +13345,13 @@
         <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13404,7 +13401,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13419,16 +13416,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13436,10 +13433,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13465,13 +13462,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13521,7 +13518,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13536,16 +13533,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13553,10 +13550,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13582,13 +13579,13 @@
         <v>105</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="N95" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13638,7 +13635,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13653,16 +13650,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN95" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13670,10 +13667,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13699,16 +13696,16 @@
         <v>299</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>302</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13757,7 +13754,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13772,16 +13769,16 @@
         <v>304</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13789,10 +13786,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13815,19 +13812,19 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13876,7 +13873,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13888,19 +13885,19 @@
         <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AK97" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AK97" t="s" s="2">
+      <c r="AL97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13908,10 +13905,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13937,16 +13934,16 @@
         <v>173</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13974,11 +13971,11 @@
         <v>267</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="Z98" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13995,7 +13992,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14010,16 +14007,16 @@
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AL98" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AL98" t="s" s="2">
+      <c r="AM98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14027,10 +14024,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14053,19 +14050,19 @@
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N99" t="s" s="2">
+      <c r="O99" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14114,7 +14111,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14129,27 +14126,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL99" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL99" t="s" s="2">
+      <c r="AM99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN99" t="s" s="2">
+      <c r="AO99" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14172,19 +14169,19 @@
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14233,7 +14230,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14248,7 +14245,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>109</v>
@@ -14257,7 +14254,7 @@
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14265,10 +14262,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14303,7 +14300,7 @@
         <v>240</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>81</v>
@@ -14352,7 +14349,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14384,10 +14381,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14413,16 +14410,16 @@
         <v>273</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -14451,7 +14448,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14469,7 +14466,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14484,16 +14481,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AL102" t="s" s="2">
+      <c r="AM102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14501,10 +14498,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14527,19 +14524,19 @@
         <v>81</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -14588,7 +14585,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14603,7 +14600,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>109</v>
@@ -14612,7 +14609,7 @@
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14620,10 +14617,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14646,19 +14643,19 @@
         <v>81</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -14707,7 +14704,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14719,10 +14716,10 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AK104" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>109</v>
@@ -14731,7 +14728,7 @@
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14739,10 +14736,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14765,19 +14762,19 @@
         <v>81</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="N105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14826,7 +14823,7 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14838,10 +14835,10 @@
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AK105" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>109</v>
@@ -14858,10 +14855,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14973,10 +14970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15090,13 +15087,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>81</v>
@@ -15118,13 +15115,13 @@
         <v>81</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="M108" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -15207,13 +15204,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>81</v>
@@ -15235,13 +15232,13 @@
         <v>81</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15324,14 +15321,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15353,10 +15350,10 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>115</v>
@@ -15411,7 +15408,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15443,10 +15440,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15472,16 +15469,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15509,16 +15506,16 @@
         <v>153</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="Z111" t="s" s="2">
+      <c r="AA111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB111" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
@@ -15528,7 +15525,7 @@
         <v>118</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15543,7 +15540,7 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>109</v>
@@ -15552,7 +15549,7 @@
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15560,13 +15557,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C112" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>81</v>
@@ -15591,16 +15588,16 @@
         <v>273</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="M112" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O112" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15629,7 +15626,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15647,7 +15644,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15662,7 +15659,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15671,7 +15668,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15679,13 +15676,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C113" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>81</v>
@@ -15710,16 +15707,16 @@
         <v>273</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M113" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O113" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15748,7 +15745,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15766,7 +15763,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15781,7 +15778,7 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15790,7 +15787,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15798,10 +15795,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15824,19 +15821,19 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15885,7 +15882,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15900,16 +15897,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15917,10 +15914,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15943,19 +15940,19 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M115" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="N115" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -16004,7 +16001,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16016,19 +16013,19 @@
         <v>101</v>
       </c>
       <c r="AJ115" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AK115" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AK115" t="s" s="2">
+      <c r="AL115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16036,10 +16033,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16062,19 +16059,19 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>240</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16123,7 +16120,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16138,7 +16135,7 @@
         <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>109</v>
@@ -16147,7 +16144,7 @@
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16155,10 +16152,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16184,16 +16181,16 @@
         <v>173</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M117" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O117" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -16221,11 +16218,11 @@
         <v>267</v>
       </c>
       <c r="Y117" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z117" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="Z117" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16242,7 +16239,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16257,7 +16254,7 @@
         <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>109</v>
@@ -16266,7 +16263,7 @@
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16274,10 +16271,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16303,16 +16300,16 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>81</v>
@@ -16361,7 +16358,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16370,13 +16367,13 @@
         <v>89</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>109</v>
@@ -16385,7 +16382,7 @@
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16393,10 +16390,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16422,10 +16419,10 @@
         <v>299</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>302</v>
@@ -16478,7 +16475,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16493,7 +16490,7 @@
         <v>304</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>109</v>
@@ -16502,7 +16499,7 @@
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16510,10 +16507,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16536,19 +16533,19 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="N120" t="s" s="2">
+      <c r="O120" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16597,7 +16594,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16612,10 +16609,10 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
@@ -16629,10 +16626,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16744,10 +16741,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16861,14 +16858,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16890,10 +16887,10 @@
         <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N123" t="s" s="2">
         <v>115</v>
@@ -16948,7 +16945,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16980,10 +16977,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17009,16 +17006,16 @@
         <v>273</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M124" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="M124" t="s" s="2">
+      <c r="N124" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17067,7 +17064,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>89</v>
@@ -17082,16 +17079,16 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AL124" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="AL124" t="s" s="2">
+      <c r="AM124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17099,10 +17096,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17125,19 +17122,19 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="N125" t="s" s="2">
+      <c r="O125" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17186,7 +17183,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17201,16 +17198,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AL125" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="AL125" t="s" s="2">
+      <c r="AM125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17218,14 +17215,14 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17244,16 +17241,16 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17303,7 +17300,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17318,7 +17315,7 @@
         <v>313</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
@@ -17327,7 +17324,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17335,10 +17332,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17361,19 +17358,19 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L127" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L127" t="s" s="2">
+      <c r="M127" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="N127" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="N127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17422,7 +17419,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17437,10 +17434,10 @@
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
@@ -17454,10 +17451,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17480,19 +17477,19 @@
         <v>90</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L128" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M128" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="M128" t="s" s="2">
+      <c r="N128" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="N128" t="s" s="2">
+      <c r="O128" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>81</v>
@@ -17541,7 +17538,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17556,7 +17553,7 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17573,10 +17570,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17688,10 +17685,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17805,14 +17802,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17834,10 +17831,10 @@
         <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M131" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>115</v>
@@ -17892,7 +17889,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17924,10 +17921,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17950,16 +17947,16 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="L132" t="s" s="2">
+      <c r="M132" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="M132" t="s" s="2">
+      <c r="N132" t="s" s="2">
         <v>672</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18009,7 +18006,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>89</v>
@@ -18033,7 +18030,7 @@
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18041,10 +18038,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18070,13 +18067,13 @@
         <v>173</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M133" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="M133" t="s" s="2">
-        <v>677</v>
-      </c>
       <c r="N133" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
@@ -18105,11 +18102,11 @@
         <v>267</v>
       </c>
       <c r="Y133" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="Z133" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="Z133" t="s" s="2">
-        <v>678</v>
-      </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18126,7 +18123,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18141,7 +18138,7 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>109</v>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T10:12:17+00:00</t>
+    <t>2024-02-05T11:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,14 +642,14 @@
     <t>nationality</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-nationality}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-nationality}
 </t>
   </si>
   <si>
-    <t>FR Core Patient Nationalité</t>
-  </si>
-  <si>
-    <t>Nationalité du patient</t>
+    <t>Nationality</t>
+  </si>
+  <si>
+    <t>The nationality of the patient.</t>
   </si>
   <si>
     <t>Patient.extension:identityReliability</t>
@@ -883,7 +883,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-patient-identifier-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1031,7 +1031,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INS-C"/&gt;
     &lt;display value="Identifiant National de Santé Calculé"/&gt;
   &lt;/coding&gt;
@@ -1082,7 +1082,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="NDP"/&gt;
     &lt;display value="Identifiant du patient au Dossier Pharmaceutique"/&gt;
   &lt;/coding&gt;
@@ -1845,7 +1845,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
   </si>
   <si>
     <t>Patient.contact.relationship:RelatedPerson</t>
@@ -1857,7 +1857,7 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2487,7 +2487,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.37109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.0703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="75.2109375" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T11:48:42+00:00</t>
+    <t>2024-02-12T13:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5341" uniqueCount="691">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1002,13 +1002,63 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
+    <t>Patient.identifier:NSS</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.use</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.type</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0203"/&gt;
+    &lt;code value="NH"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.system</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.8</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS.assigner</t>
+  </si>
+  <si>
     <t>Patient.identifier:INS-C</t>
   </si>
   <si>
     <t>INS-C</t>
-  </si>
-  <si>
-    <t>An identifier for this patient</t>
   </si>
   <si>
     <t>Computed National Health Identifier | Identifiant National de Santé Calculé à partir des éléments de la carte vitale</t>
@@ -1038,12 +1088,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
     <t>Patient.identifier:INS-C.system</t>
   </si>
   <si>
@@ -1502,9 +1546,6 @@
   </si>
   <si>
     <t>Patient.name:officialName.use</t>
-  </si>
-  <si>
-    <t>official</t>
   </si>
   <si>
     <t>Patient.name:officialName.text</t>
@@ -2459,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO133"/>
+  <dimension ref="A1:AO142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.79296875" customWidth="true" bestFit="true"/>
@@ -6857,7 +6898,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6875,7 +6916,7 @@
         <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>252</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
@@ -6960,7 +7001,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>260</v>
@@ -7075,7 +7116,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>261</v>
@@ -7192,7 +7233,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>262</v>
@@ -7240,7 +7281,7 @@
         <v>81</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>81</v>
@@ -7311,7 +7352,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>272</v>
@@ -7343,7 +7384,7 @@
         <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>276</v>
@@ -7359,7 +7400,7 @@
         <v>81</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>81</v>
@@ -7377,10 +7418,10 @@
         <v>153</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7430,7 +7471,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>281</v>
@@ -7478,7 +7519,7 @@
         <v>81</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>286</v>
@@ -7549,7 +7590,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>290</v>
@@ -7666,7 +7707,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>298</v>
@@ -7783,7 +7824,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>307</v>
@@ -7900,13 +7941,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>249</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>81</v>
@@ -7916,7 +7957,7 @@
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7931,7 +7972,7 @@
         <v>250</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>252</v>
@@ -8019,7 +8060,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>260</v>
@@ -8134,7 +8175,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>261</v>
@@ -8251,7 +8292,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>262</v>
@@ -8299,7 +8340,7 @@
         <v>81</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>81</v>
@@ -8402,7 +8443,7 @@
         <v>274</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>275</v>
+        <v>334</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>276</v>
@@ -8435,9 +8476,11 @@
       <c r="X51" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8498,7 +8541,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
@@ -8991,7 +9034,7 @@
         <v>348</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
+        <v>252</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -9356,7 +9399,7 @@
         <v>81</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>81</v>
@@ -9427,7 +9470,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>272</v>
@@ -9475,7 +9518,7 @@
         <v>81</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>81</v>
@@ -9493,10 +9536,10 @@
         <v>153</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9546,7 +9589,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>281</v>
@@ -9594,7 +9637,7 @@
         <v>81</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>286</v>
@@ -10032,7 +10075,7 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -10050,7 +10093,7 @@
         <v>361</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -10415,7 +10458,7 @@
         <v>81</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>323</v>
+        <v>365</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>81</v>
@@ -10486,7 +10529,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>272</v>
@@ -10534,7 +10577,7 @@
         <v>81</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>81</v>
@@ -10552,10 +10595,10 @@
         <v>153</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10605,7 +10648,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>281</v>
@@ -10724,7 +10767,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>290</v>
@@ -10841,7 +10884,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>298</v>
@@ -10958,7 +11001,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>307</v>
@@ -11075,12 +11118,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11089,38 +11134,34 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>372</v>
+        <v>250</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>376</v>
+        <v>253</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q74" t="s" s="2">
-        <v>377</v>
-      </c>
+      <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
         <v>81</v>
       </c>
@@ -11164,13 +11205,13 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>371</v>
+        <v>249</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>101</v>
@@ -11179,16 +11220,16 @@
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>378</v>
+        <v>256</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>109</v>
+        <v>257</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>379</v>
+        <v>258</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>81</v>
+        <v>259</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>81</v>
@@ -11196,10 +11237,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11210,7 +11251,7 @@
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>81</v>
@@ -11219,23 +11260,19 @@
         <v>81</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>381</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>81</v>
       </c>
@@ -11271,41 +11308,43 @@
         <v>81</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC75" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>81</v>
@@ -11313,16 +11352,14 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11338,23 +11375,21 @@
         <v>81</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>392</v>
+        <v>112</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>393</v>
+        <v>113</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>394</v>
+        <v>114</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11390,19 +11425,19 @@
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>380</v>
+        <v>119</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11414,19 +11449,19 @@
         <v>101</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>387</v>
+        <v>103</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>81</v>
@@ -11434,10 +11469,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>396</v>
+        <v>262</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11454,22 +11489,26 @@
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>106</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11478,7 +11517,7 @@
         <v>81</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>81</v>
@@ -11493,13 +11532,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -11517,7 +11556,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11526,13 +11565,13 @@
         <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>109</v>
+        <v>271</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>81</v>
@@ -11541,7 +11580,7 @@
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>81</v>
@@ -11549,21 +11588,21 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>398</v>
+        <v>272</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>81</v>
@@ -11572,21 +11611,23 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11595,7 +11636,7 @@
         <v>81</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>81</v>
+        <v>379</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>81</v>
@@ -11610,46 +11651,46 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>81</v>
+        <v>325</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>119</v>
+        <v>279</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>81</v>
@@ -11658,7 +11699,7 @@
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>81</v>
@@ -11666,10 +11707,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>400</v>
+        <v>281</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11686,25 +11727,25 @@
         <v>81</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>401</v>
+        <v>282</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>402</v>
+        <v>283</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>404</v>
+        <v>285</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
@@ -11714,10 +11755,10 @@
         <v>81</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>352</v>
+        <v>81</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>81</v>
+        <v>286</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>81</v>
@@ -11729,13 +11770,13 @@
         <v>81</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>81</v>
@@ -11753,7 +11794,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>407</v>
+        <v>287</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11768,7 +11809,7 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>408</v>
+        <v>288</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>81</v>
@@ -11777,7 +11818,7 @@
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>409</v>
+        <v>289</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>81</v>
@@ -11785,10 +11826,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>411</v>
+        <v>290</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11796,7 +11837,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
@@ -11814,17 +11855,15 @@
         <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>412</v>
+        <v>291</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11836,7 +11875,7 @@
         <v>81</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>81</v>
@@ -11872,7 +11911,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>416</v>
+        <v>295</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11887,7 +11926,7 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>417</v>
+        <v>296</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>81</v>
@@ -11896,7 +11935,7 @@
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>418</v>
+        <v>297</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>81</v>
@@ -11904,14 +11943,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>419</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>420</v>
+        <v>298</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11930,16 +11969,16 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>422</v>
+        <v>300</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>423</v>
+        <v>301</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>424</v>
+        <v>302</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11989,7 +12028,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>425</v>
+        <v>303</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12001,10 +12040,10 @@
         <v>101</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>426</v>
+        <v>305</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>81</v>
@@ -12013,7 +12052,7 @@
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>427</v>
+        <v>306</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>81</v>
@@ -12021,21 +12060,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>428</v>
+        <v>383</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>429</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>81</v>
@@ -12047,16 +12086,16 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>105</v>
+        <v>308</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>431</v>
+        <v>309</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>432</v>
+        <v>310</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>433</v>
+        <v>311</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12106,22 +12145,22 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>434</v>
+        <v>312</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>313</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>435</v>
+        <v>314</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>81</v>
@@ -12130,7 +12169,7 @@
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>436</v>
+        <v>315</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>81</v>
@@ -12138,10 +12177,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>437</v>
+        <v>384</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12152,34 +12191,38 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>105</v>
+        <v>385</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>440</v>
+        <v>387</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="Q83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="R83" t="s" s="2">
         <v>81</v>
       </c>
@@ -12223,13 +12266,13 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>101</v>
@@ -12238,16 +12281,16 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>443</v>
+        <v>391</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>81</v>
@@ -12255,10 +12298,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>445</v>
+        <v>393</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,18 +12324,20 @@
         <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>105</v>
+        <v>394</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -12328,19 +12373,17 @@
         <v>81</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12355,16 +12398,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>451</v>
+        <v>402</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>81</v>
@@ -12372,12 +12415,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>452</v>
+        <v>403</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C85" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D85" t="s" s="2">
         <v>81</v>
       </c>
@@ -12386,7 +12431,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>81</v>
@@ -12398,19 +12443,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>299</v>
+        <v>405</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>454</v>
+        <v>406</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>455</v>
+        <v>407</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>456</v>
+        <v>398</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -12459,31 +12504,31 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>457</v>
+        <v>393</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>458</v>
+        <v>400</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>81</v>
@@ -12491,14 +12536,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12507,7 +12550,7 @@
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -12516,23 +12559,19 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
@@ -12580,31 +12619,31 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>387</v>
+        <v>109</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>389</v>
+        <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>81</v>
@@ -12612,21 +12651,21 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>464</v>
+        <v>410</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12638,15 +12677,17 @@
         <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12683,34 +12724,34 @@
         <v>81</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>81</v>
@@ -12727,44 +12768,46 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>113</v>
+        <v>414</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>114</v>
+        <v>415</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12773,7 +12816,7 @@
         <v>81</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>81</v>
+        <v>365</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>81</v>
@@ -12788,46 +12831,46 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>119</v>
+        <v>420</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>103</v>
+        <v>421</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>81</v>
@@ -12836,7 +12879,7 @@
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>81</v>
@@ -12844,14 +12887,12 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12869,19 +12910,23 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>468</v>
+        <v>105</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12929,22 +12974,22 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>119</v>
+        <v>429</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>81</v>
+        <v>430</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>81</v>
@@ -12953,7 +12998,7 @@
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>81</v>
@@ -12961,18 +13006,18 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>471</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>400</v>
+        <v>433</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12981,26 +13026,24 @@
         <v>81</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>81</v>
       </c>
@@ -13009,7 +13052,7 @@
         <v>81</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>81</v>
@@ -13024,13 +13067,13 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -13048,7 +13091,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13063,7 +13106,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>408</v>
+        <v>439</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>81</v>
@@ -13072,7 +13115,7 @@
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>409</v>
+        <v>440</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>81</v>
@@ -13080,21 +13123,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>411</v>
+        <v>442</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>81</v>
@@ -13109,17 +13152,15 @@
         <v>105</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
       </c>
@@ -13167,13 +13208,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>101</v>
@@ -13182,7 +13223,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>81</v>
@@ -13191,7 +13232,7 @@
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>418</v>
+        <v>449</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>81</v>
@@ -13199,21 +13240,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>421</v>
+        <v>81</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>81</v>
@@ -13228,13 +13269,13 @@
         <v>105</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13284,13 +13325,13 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>101</v>
@@ -13299,7 +13340,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>426</v>
+        <v>456</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>81</v>
@@ -13308,7 +13349,7 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>81</v>
@@ -13316,21 +13357,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>81</v>
@@ -13345,13 +13386,13 @@
         <v>105</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>431</v>
+        <v>460</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13401,7 +13442,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13416,7 +13457,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>81</v>
@@ -13425,7 +13466,7 @@
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>81</v>
@@ -13433,10 +13474,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13447,7 +13488,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>81</v>
@@ -13459,18 +13500,20 @@
         <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>105</v>
+        <v>299</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -13518,22 +13561,22 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>81</v>
@@ -13542,7 +13585,7 @@
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>81</v>
@@ -13550,12 +13593,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13576,18 +13621,20 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>105</v>
+        <v>405</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>81</v>
       </c>
@@ -13635,7 +13682,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>449</v>
+        <v>393</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13650,16 +13697,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>81</v>
+        <v>401</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>451</v>
+        <v>402</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>81</v>
@@ -13667,10 +13714,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13690,23 +13737,19 @@
         <v>81</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>454</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13754,7 +13797,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>457</v>
+        <v>108</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13763,13 +13806,13 @@
         <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>458</v>
+        <v>109</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>81</v>
@@ -13778,7 +13821,7 @@
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>459</v>
+        <v>81</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>81</v>
@@ -13786,14 +13829,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>479</v>
+        <v>411</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13812,20 +13855,18 @@
         <v>81</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>480</v>
+        <v>112</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>481</v>
+        <v>113</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>482</v>
+        <v>114</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
       </c>
@@ -13861,19 +13902,19 @@
         <v>81</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>479</v>
+        <v>119</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13885,10 +13926,10 @@
         <v>101</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>485</v>
+        <v>120</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>486</v>
+        <v>103</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>81</v>
@@ -13897,7 +13938,7 @@
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>81</v>
@@ -13905,12 +13946,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C98" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13928,23 +13971,19 @@
         <v>81</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>173</v>
+        <v>481</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
       </c>
@@ -13968,13 +14007,13 @@
         <v>81</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>81</v>
@@ -13992,31 +14031,31 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>488</v>
+        <v>119</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>81</v>
@@ -14024,10 +14063,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14035,7 +14074,7 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>89</v>
@@ -14044,25 +14083,25 @@
         <v>81</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>499</v>
+        <v>173</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>502</v>
+        <v>417</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>81</v>
@@ -14072,7 +14111,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14087,13 +14126,13 @@
         <v>81</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>81</v>
+        <v>418</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>81</v>
@@ -14111,7 +14150,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>498</v>
+        <v>420</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14126,27 +14165,27 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>505</v>
+        <v>422</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>507</v>
+        <v>424</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14163,25 +14202,25 @@
         <v>81</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>508</v>
+        <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>509</v>
+        <v>425</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>510</v>
+        <v>426</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>511</v>
+        <v>427</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>512</v>
+        <v>428</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -14230,7 +14269,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>507</v>
+        <v>429</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14245,16 +14284,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>513</v>
+        <v>430</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>81</v>
@@ -14262,21 +14301,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>515</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>515</v>
+        <v>433</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>81</v>
@@ -14285,23 +14324,21 @@
         <v>81</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>238</v>
+        <v>435</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>239</v>
+        <v>436</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>81</v>
       </c>
@@ -14349,13 +14386,13 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>515</v>
+        <v>438</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>101</v>
@@ -14364,7 +14401,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>242</v>
+        <v>439</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>81</v>
@@ -14373,7 +14410,7 @@
         <v>81</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>243</v>
+        <v>440</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>81</v>
@@ -14381,18 +14418,18 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>517</v>
+        <v>442</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>81</v>
+        <v>443</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -14404,23 +14441,21 @@
         <v>81</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>518</v>
+        <v>444</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>81</v>
       </c>
@@ -14444,11 +14479,13 @@
         <v>81</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>81</v>
@@ -14466,13 +14503,13 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>517</v>
+        <v>447</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>101</v>
@@ -14481,16 +14518,16 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>523</v>
+        <v>448</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>525</v>
+        <v>449</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>81</v>
@@ -14498,10 +14535,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>526</v>
+        <v>451</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14512,7 +14549,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>81</v>
@@ -14521,23 +14558,21 @@
         <v>81</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>527</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>528</v>
+        <v>452</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>529</v>
+        <v>453</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>81</v>
       </c>
@@ -14585,13 +14620,13 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>526</v>
+        <v>455</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>101</v>
@@ -14600,16 +14635,16 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>533</v>
+        <v>457</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>81</v>
@@ -14617,10 +14652,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>534</v>
+        <v>489</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>534</v>
+        <v>459</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14640,23 +14675,21 @@
         <v>81</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>536</v>
+        <v>460</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>537</v>
+        <v>461</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>81</v>
       </c>
@@ -14704,7 +14737,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>534</v>
+        <v>462</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14716,19 +14749,19 @@
         <v>101</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>540</v>
+        <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>541</v>
+        <v>463</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>81</v>
@@ -14736,10 +14769,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>543</v>
+        <v>490</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>543</v>
+        <v>466</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14750,7 +14783,7 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>81</v>
@@ -14759,22 +14792,22 @@
         <v>81</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>544</v>
+        <v>299</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>545</v>
+        <v>467</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>546</v>
+        <v>468</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>547</v>
+        <v>302</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>548</v>
+        <v>469</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -14823,31 +14856,31 @@
         <v>81</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>543</v>
+        <v>470</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>549</v>
+        <v>304</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>550</v>
+        <v>471</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>81</v>
+        <v>472</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>81</v>
@@ -14855,10 +14888,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>551</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>551</v>
+        <v>491</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14869,7 +14902,7 @@
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>81</v>
@@ -14881,16 +14914,20 @@
         <v>81</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>105</v>
+        <v>492</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>106</v>
+        <v>493</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>81</v>
       </c>
@@ -14938,22 +14975,22 @@
         <v>81</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>108</v>
+        <v>491</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>109</v>
+        <v>498</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>81</v>
@@ -14962,7 +14999,7 @@
         <v>81</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>81</v>
+        <v>499</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>81</v>
@@ -14970,21 +15007,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>81</v>
@@ -14993,21 +15030,23 @@
         <v>81</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>114</v>
+        <v>502</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>81</v>
       </c>
@@ -15031,55 +15070,55 @@
         <v>81</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>119</v>
+        <v>500</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>103</v>
+        <v>507</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>81</v>
+        <v>508</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>81</v>
+        <v>509</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>81</v>
@@ -15087,14 +15126,12 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>553</v>
+        <v>510</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15112,19 +15149,23 @@
         <v>81</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>555</v>
+        <v>511</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>556</v>
+        <v>512</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
       </c>
@@ -15172,46 +15213,44 @@
         <v>81</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>119</v>
+        <v>510</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>81</v>
+        <v>515</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>81</v>
+        <v>516</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>81</v>
+        <v>517</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15226,22 +15265,26 @@
         <v>81</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>560</v>
+        <v>520</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>561</v>
+        <v>521</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
       </c>
@@ -15289,31 +15332,31 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>119</v>
+        <v>519</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>81</v>
+        <v>525</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>81</v>
+        <v>526</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15321,14 +15364,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>563</v>
+        <v>527</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15341,25 +15384,25 @@
         <v>81</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>565</v>
+        <v>238</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>566</v>
+        <v>239</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>247</v>
+        <v>528</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15408,7 +15451,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>567</v>
+        <v>527</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15420,10 +15463,10 @@
         <v>101</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>81</v>
@@ -15432,7 +15475,7 @@
         <v>81</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>81</v>
@@ -15440,10 +15483,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15451,7 +15494,7 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>89</v>
@@ -15469,16 +15512,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>571</v>
+        <v>533</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15505,33 +15548,33 @@
       <c r="X111" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y111" t="s" s="2">
-        <v>572</v>
-      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>573</v>
+        <v>534</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AC111" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>101</v>
@@ -15540,16 +15583,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>575</v>
+        <v>535</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>109</v>
+        <v>536</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15557,14 +15600,12 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15585,19 +15626,19 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>273</v>
+        <v>539</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>570</v>
+        <v>541</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>571</v>
+        <v>543</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15622,11 +15663,13 @@
         <v>81</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>580</v>
+        <v>81</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
@@ -15644,13 +15687,13 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>101</v>
@@ -15659,7 +15702,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>575</v>
+        <v>544</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15668,7 +15711,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>576</v>
+        <v>545</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15676,14 +15719,12 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>581</v>
+        <v>546</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>81</v>
       </c>
@@ -15692,7 +15733,7 @@
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>81</v>
@@ -15704,19 +15745,19 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>273</v>
+        <v>547</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>583</v>
+        <v>548</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15741,11 +15782,13 @@
         <v>81</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y113" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z113" t="s" s="2">
-        <v>584</v>
+        <v>81</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>81</v>
@@ -15763,7 +15806,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15775,10 +15818,10 @@
         <v>101</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>552</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15787,7 +15830,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15795,10 +15838,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15809,7 +15852,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>81</v>
@@ -15821,19 +15864,19 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>381</v>
+        <v>556</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>586</v>
+        <v>557</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>587</v>
+        <v>558</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>588</v>
+        <v>559</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15882,31 +15925,31 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>102</v>
+        <v>561</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>590</v>
+        <v>562</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>81</v>
@@ -15914,10 +15957,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>592</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15928,7 +15971,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>81</v>
@@ -15940,20 +15983,16 @@
         <v>81</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>481</v>
+        <v>106</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>81</v>
       </c>
@@ -16001,22 +16040,22 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>592</v>
+        <v>108</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>486</v>
+        <v>109</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>81</v>
@@ -16025,7 +16064,7 @@
         <v>81</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>81</v>
@@ -16033,21 +16072,21 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>81</v>
@@ -16059,20 +16098,18 @@
         <v>81</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>595</v>
+        <v>112</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>596</v>
+        <v>113</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>597</v>
+        <v>114</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>81</v>
       </c>
@@ -16108,43 +16145,43 @@
         <v>81</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>594</v>
+        <v>119</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>599</v>
+        <v>103</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>600</v>
+        <v>81</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>81</v>
@@ -16152,12 +16189,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>601</v>
+        <v>565</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16178,20 +16217,16 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>173</v>
+        <v>567</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>489</v>
+        <v>568</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>81</v>
       </c>
@@ -16215,13 +16250,13 @@
         <v>81</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>267</v>
+        <v>81</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>81</v>
@@ -16239,31 +16274,31 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>601</v>
+        <v>119</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>604</v>
+        <v>81</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>81</v>
@@ -16271,12 +16306,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>605</v>
+        <v>570</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16297,20 +16334,16 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>308</v>
+        <v>572</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>606</v>
+        <v>573</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>81</v>
       </c>
@@ -16358,31 +16391,31 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>605</v>
+        <v>119</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>610</v>
+        <v>101</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>313</v>
+        <v>120</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>611</v>
+        <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>612</v>
+        <v>81</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>81</v>
@@ -16390,44 +16423,46 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>613</v>
+        <v>575</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>613</v>
+        <v>575</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>81</v>
+        <v>576</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>299</v>
+        <v>112</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>614</v>
+        <v>577</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>615</v>
+        <v>578</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
       </c>
@@ -16475,31 +16510,31 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>613</v>
+        <v>579</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>304</v>
+        <v>120</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>616</v>
+        <v>103</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>617</v>
+        <v>81</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>81</v>
@@ -16507,10 +16542,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>618</v>
+        <v>580</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>618</v>
+        <v>580</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16518,10 +16553,10 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>81</v>
@@ -16533,19 +16568,19 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>544</v>
+        <v>273</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>619</v>
+        <v>581</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>620</v>
+        <v>582</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>621</v>
+        <v>532</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16570,31 +16605,29 @@
         <v>81</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>81</v>
+        <v>584</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>81</v>
+        <v>585</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>618</v>
+        <v>580</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16609,16 +16642,16 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>623</v>
+        <v>587</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>624</v>
+        <v>109</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>81</v>
@@ -16626,12 +16659,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>625</v>
+        <v>589</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16652,16 +16687,20 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>106</v>
+        <v>591</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
       </c>
@@ -16685,13 +16724,11 @@
         <v>81</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>81</v>
+        <v>592</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16709,31 +16746,31 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>108</v>
+        <v>580</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AL121" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AL121" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="AM121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>81</v>
@@ -16741,21 +16778,23 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>626</v>
+        <v>593</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="D122" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>81</v>
@@ -16767,18 +16806,20 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>113</v>
+        <v>595</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>114</v>
+        <v>582</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
       </c>
@@ -16802,31 +16843,29 @@
         <v>81</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>81</v>
+        <v>596</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC122" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE122" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>119</v>
+        <v>580</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16838,19 +16877,19 @@
         <v>101</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>103</v>
+        <v>587</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>81</v>
+        <v>588</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>81</v>
@@ -16858,45 +16897,45 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>112</v>
+        <v>394</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>565</v>
+        <v>598</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>115</v>
+        <v>600</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>247</v>
+        <v>601</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16945,22 +16984,22 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>103</v>
+        <v>602</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>81</v>
@@ -16969,7 +17008,7 @@
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>81</v>
+        <v>603</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -16977,10 +17016,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16988,10 +17027,10 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>81</v>
@@ -17003,19 +17042,19 @@
         <v>81</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>273</v>
+        <v>492</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>629</v>
+        <v>493</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>630</v>
+        <v>494</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>632</v>
+        <v>496</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>81</v>
@@ -17040,13 +17079,13 @@
         <v>81</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>81</v>
@@ -17064,31 +17103,31 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>497</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>633</v>
+        <v>498</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>634</v>
+        <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>635</v>
+        <v>499</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>81</v>
@@ -17096,10 +17135,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17122,19 +17161,19 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>372</v>
+        <v>607</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>637</v>
+        <v>608</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>638</v>
+        <v>609</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>639</v>
+        <v>240</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17183,7 +17222,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17198,16 +17237,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>642</v>
+        <v>109</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17215,21 +17254,21 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>645</v>
+        <v>81</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>81</v>
@@ -17241,18 +17280,20 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>646</v>
+        <v>173</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>647</v>
+        <v>501</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>648</v>
+        <v>614</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="O126" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
       </c>
@@ -17276,13 +17317,13 @@
         <v>81</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>81</v>
+        <v>506</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -17300,22 +17341,22 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>650</v>
+        <v>507</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>109</v>
@@ -17324,7 +17365,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>651</v>
+        <v>616</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17332,10 +17373,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>652</v>
+        <v>617</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>652</v>
+        <v>617</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17355,22 +17396,22 @@
         <v>81</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>653</v>
+        <v>308</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>654</v>
+        <v>618</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>655</v>
+        <v>619</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>656</v>
+        <v>620</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>657</v>
+        <v>621</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17419,7 +17460,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>652</v>
+        <v>617</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17428,22 +17469,22 @@
         <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>101</v>
+        <v>622</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>658</v>
+        <v>109</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>81</v>
+        <v>624</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17451,10 +17492,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>659</v>
+        <v>625</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>659</v>
+        <v>625</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17465,32 +17506,30 @@
         <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>544</v>
+        <v>299</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>660</v>
+        <v>626</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>661</v>
+        <v>627</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>663</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>81</v>
       </c>
@@ -17538,22 +17577,22 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>659</v>
+        <v>625</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>304</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>664</v>
+        <v>628</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17562,7 +17601,7 @@
         <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>81</v>
+        <v>629</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -17570,10 +17609,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>665</v>
+        <v>630</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>665</v>
+        <v>630</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17584,7 +17623,7 @@
         <v>79</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>81</v>
@@ -17596,16 +17635,20 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>105</v>
+        <v>556</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>106</v>
+        <v>631</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>634</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
       </c>
@@ -17653,25 +17696,25 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>108</v>
+        <v>630</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>109</v>
+        <v>635</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>81</v>
+        <v>636</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>81</v>
@@ -17685,21 +17728,21 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>666</v>
+        <v>637</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>666</v>
+        <v>637</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>81</v>
@@ -17711,17 +17754,15 @@
         <v>81</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>81</v>
@@ -17758,34 +17799,34 @@
         <v>81</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>81</v>
@@ -17802,14 +17843,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>564</v>
+        <v>111</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17822,26 +17863,24 @@
         <v>81</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>112</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>565</v>
+        <v>113</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>566</v>
+        <v>114</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="O131" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>81</v>
       </c>
@@ -17877,19 +17916,19 @@
         <v>81</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>567</v>
+        <v>119</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17921,44 +17960,46 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>81</v>
+        <v>576</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J132" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>669</v>
+        <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>670</v>
+        <v>577</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>671</v>
+        <v>578</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>81</v>
       </c>
@@ -18006,31 +18047,31 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>668</v>
+        <v>579</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>313</v>
+        <v>120</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>673</v>
+        <v>81</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>81</v>
@@ -18038,10 +18079,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18061,21 +18102,23 @@
         <v>81</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
       </c>
@@ -18099,13 +18142,13 @@
         <v>81</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>267</v>
+        <v>177</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>676</v>
+        <v>178</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>677</v>
+        <v>179</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>81</v>
@@ -18123,7 +18166,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18138,18 +18181,1077 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="P134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="O136" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="P136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="P137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="AL133" t="s" s="2">
+      <c r="B139" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO139" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO140" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL141" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AM133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO133" t="s" s="2">
+      <c r="AM141" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AO141" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5341" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5341" uniqueCount="692">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:03:57+00:00</t>
+    <t>2024-03-04T10:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile of the Patient resource for France | Profil de la ressource Patient pour l'usage en France
-This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions | Ce profil spécifie les identifiants de patient utilisés en France. Il utilise des extensions internationales (birthplace et nationalité) et ajoute des extensions propres à la France.</t>
+    <t>Profile of the Patient resource for France. This profile specifies the patient's identifiers for France. It uses international extensions (birtplace and nationality) and adds specific French extensions. (fr: Ce profil spécifie les identifiants de patient utilisés en France. Il utilise des extensions internationales (birthplace et nationalité) et ajoute des extensions propres à la France.)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1633,6 +1632,9 @@
   </si>
   <si>
     <t>The date of birth for the french patient checked with the INSitelservice | Date de naissance du patient. Dans le cas d'une identité récupérée du téléservice INSi, la date de naissance est modifiée selon les règles du RNIV dans le cas de dates exceptionnelles.</t>
+  </si>
+  <si>
+    <t>The date of birth for the individual.</t>
   </si>
   <si>
     <t>At least an estimated year should be provided as a guess if the real DOB is unknown  There is a standard extension "patient-birthTime" available that should be used where Time is required (such as in maternity/infant care systems).</t>
@@ -14432,7 +14434,7 @@
         <v>89</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>81</v>
@@ -15158,13 +15160,13 @@
         <v>512</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>81</v>
@@ -15228,27 +15230,27 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15271,19 +15273,19 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -15332,7 +15334,7 @@
         <v>81</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15347,7 +15349,7 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>109</v>
@@ -15356,7 +15358,7 @@
         <v>81</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>81</v>
@@ -15364,10 +15366,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15402,7 +15404,7 @@
         <v>240</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -15451,7 +15453,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15483,10 +15485,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15512,16 +15514,16 @@
         <v>273</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15550,7 +15552,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
@@ -15568,7 +15570,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15583,16 +15585,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>81</v>
@@ -15600,10 +15602,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15626,19 +15628,19 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15687,7 +15689,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15702,7 +15704,7 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>109</v>
@@ -15711,7 +15713,7 @@
         <v>81</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>81</v>
@@ -15719,10 +15721,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15745,19 +15747,19 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15806,7 +15808,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15818,10 +15820,10 @@
         <v>101</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>109</v>
@@ -15830,7 +15832,7 @@
         <v>81</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>81</v>
@@ -15838,10 +15840,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15864,19 +15866,19 @@
         <v>81</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15925,7 +15927,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15937,10 +15939,10 @@
         <v>101</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>109</v>
@@ -15957,10 +15959,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16072,10 +16074,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16189,13 +16191,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="B117" t="s" s="2">
-        <v>564</v>
-      </c>
       <c r="C117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>81</v>
@@ -16217,13 +16219,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16306,13 +16308,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>81</v>
@@ -16334,13 +16336,13 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16423,14 +16425,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16452,10 +16454,10 @@
         <v>112</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>115</v>
@@ -16510,7 +16512,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16542,10 +16544,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16571,16 +16573,16 @@
         <v>273</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>81</v>
@@ -16608,16 +16610,16 @@
         <v>153</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -16627,7 +16629,7 @@
         <v>118</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16642,7 +16644,7 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>109</v>
@@ -16651,7 +16653,7 @@
         <v>81</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>81</v>
@@ -16659,13 +16661,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -16690,16 +16692,16 @@
         <v>273</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>81</v>
@@ -16728,7 +16730,7 @@
       </c>
       <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>81</v>
@@ -16746,7 +16748,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16761,7 +16763,7 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>109</v>
@@ -16770,7 +16772,7 @@
         <v>81</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>81</v>
@@ -16778,13 +16780,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>81</v>
@@ -16809,16 +16811,16 @@
         <v>273</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>81</v>
@@ -16847,7 +16849,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>81</v>
@@ -16865,7 +16867,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16880,7 +16882,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>109</v>
@@ -16889,7 +16891,7 @@
         <v>81</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>81</v>
@@ -16897,10 +16899,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16926,16 +16928,16 @@
         <v>394</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>81</v>
@@ -16984,7 +16986,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16999,7 +17001,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>81</v>
@@ -17008,7 +17010,7 @@
         <v>81</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -17016,10 +17018,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17051,7 +17053,7 @@
         <v>494</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>496</v>
@@ -17103,7 +17105,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17135,10 +17137,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17161,19 +17163,19 @@
         <v>81</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>240</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17222,7 +17224,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17237,7 +17239,7 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>109</v>
@@ -17246,7 +17248,7 @@
         <v>81</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -17254,10 +17256,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17286,13 +17288,13 @@
         <v>501</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>454</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -17341,7 +17343,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17365,7 +17367,7 @@
         <v>81</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>81</v>
@@ -17373,10 +17375,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17402,16 +17404,16 @@
         <v>308</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>81</v>
@@ -17460,7 +17462,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -17469,13 +17471,13 @@
         <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>313</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>109</v>
@@ -17484,7 +17486,7 @@
         <v>81</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -17492,10 +17494,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17521,10 +17523,10 @@
         <v>299</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>302</v>
@@ -17577,7 +17579,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17592,7 +17594,7 @@
         <v>304</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AL128" t="s" s="2">
         <v>109</v>
@@ -17601,7 +17603,7 @@
         <v>81</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>81</v>
@@ -17609,10 +17611,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17635,19 +17637,19 @@
         <v>81</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>81</v>
@@ -17696,7 +17698,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17711,10 +17713,10 @@
         <v>102</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>81</v>
@@ -17728,10 +17730,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17843,10 +17845,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17960,14 +17962,14 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17989,10 +17991,10 @@
         <v>112</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>115</v>
@@ -18047,7 +18049,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18079,10 +18081,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18108,16 +18110,16 @@
         <v>273</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18166,7 +18168,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>89</v>
@@ -18181,16 +18183,16 @@
         <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>81</v>
@@ -18198,10 +18200,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18227,16 +18229,16 @@
         <v>385</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18285,7 +18287,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18300,16 +18302,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>81</v>
@@ -18317,14 +18319,14 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18343,16 +18345,16 @@
         <v>81</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -18402,7 +18404,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18417,7 +18419,7 @@
         <v>313</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>109</v>
@@ -18426,7 +18428,7 @@
         <v>81</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>81</v>
@@ -18434,10 +18436,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18460,19 +18462,19 @@
         <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18521,7 +18523,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18536,10 +18538,10 @@
         <v>313</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AM136" t="s" s="2">
         <v>81</v>
@@ -18553,10 +18555,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18579,19 +18581,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -18640,7 +18642,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18655,7 +18657,7 @@
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>109</v>
@@ -18672,10 +18674,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18787,10 +18789,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18904,14 +18906,14 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18933,10 +18935,10 @@
         <v>112</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>115</v>
@@ -18991,7 +18993,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19023,10 +19025,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19049,16 +19051,16 @@
         <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19108,7 +19110,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>89</v>
@@ -19132,7 +19134,7 @@
         <v>81</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -19140,10 +19142,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19169,10 +19171,10 @@
         <v>173</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>454</v>
@@ -19204,10 +19206,10 @@
         <v>267</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>81</v>
@@ -19225,7 +19227,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>89</v>
@@ -19240,7 +19242,7 @@
         <v>102</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>109</v>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/main/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
